--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37210-2026 artfynd.xlsx
+++ b/artfynd/A 37210-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136965252</v>
       </c>
       <c r="B2" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
